--- a/data/trans_dic/P44A$endoscopia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 78,17</t>
+          <t>24,67; 76,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,71; 70,55</t>
+          <t>31,95; 69,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,62; 56,39</t>
+          <t>39,95; 55,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 79,4</t>
+          <t>15,54; 74,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 81,34</t>
+          <t>11,37; 76,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 39,91</t>
+          <t>23,59; 40,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 66,63</t>
+          <t>28,07; 68,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 65,8</t>
+          <t>34,5; 68,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 48,17</t>
+          <t>36,41; 48,22</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,74; 79,75</t>
+          <t>31,78; 82,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 50,98</t>
+          <t>11,72; 47,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,02; 51,02</t>
+          <t>31,62; 50,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,9</t>
+          <t>0,0; 70,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 50,43</t>
+          <t>29,82; 49,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,27; 66,15</t>
+          <t>24,82; 66,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 51,56</t>
+          <t>16,75; 52,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,9; 47,85</t>
+          <t>32,1; 47,23</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,46; 89,52</t>
+          <t>51,76; 89,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 72,86</t>
+          <t>33,76; 73,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,77; 96,82</t>
+          <t>38,65; 95,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,69; 83,3</t>
+          <t>21,64; 89,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 86,33</t>
+          <t>14,16; 86,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,05; 53,72</t>
+          <t>29,66; 53,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,16; 84,56</t>
+          <t>51,07; 84,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,2; 73,02</t>
+          <t>39,11; 72,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,47; 94,88</t>
+          <t>38,9; 95,29</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,9; 72,01</t>
+          <t>39,03; 73,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,46; 75,21</t>
+          <t>49,29; 76,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,14; 48,72</t>
+          <t>35,69; 49,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,25; 92,82</t>
+          <t>42,62; 92,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,92; 79,15</t>
+          <t>34,67; 78,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,08; 43,48</t>
+          <t>28,31; 44,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,83; 73,3</t>
+          <t>45,87; 74,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,21; 72,84</t>
+          <t>49,62; 71,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,98; 44,94</t>
+          <t>34,77; 45,08</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,31; 100,0</t>
+          <t>36,8; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,42; 72,79</t>
+          <t>34,39; 73,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 46,23</t>
+          <t>25,62; 45,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,27; 86,75</t>
+          <t>48,22; 86,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,47; 74,55</t>
+          <t>34,23; 74,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,41; 39,02</t>
+          <t>26,62; 38,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,88; 87,18</t>
+          <t>54,42; 85,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,92; 68,17</t>
+          <t>40,44; 66,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,78; 39,4</t>
+          <t>28,43; 39,2</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,32; 81,6</t>
+          <t>10,89; 81,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,96; 82,82</t>
+          <t>48,21; 83,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,59; 74,79</t>
+          <t>42,3; 75,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,96; 49,63</t>
+          <t>36,88; 50,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,96; 82,82</t>
+          <t>48,21; 83,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,59; 74,79</t>
+          <t>42,3; 75,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,46; 50,45</t>
+          <t>37,26; 50,35</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,6; 71,36</t>
+          <t>52,35; 71,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,01; 59,97</t>
+          <t>43,79; 60,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,08; 84,92</t>
+          <t>41,03; 81,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51,67; 71,85</t>
+          <t>52,27; 71,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,85; 66,14</t>
+          <t>46,73; 67,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,87; 40,14</t>
+          <t>33,84; 40,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,2; 69,03</t>
+          <t>54,59; 67,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,89; 60,24</t>
+          <t>47,18; 59,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,15; 73,54</t>
+          <t>38,82; 73,08</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4630; 14973</t>
+          <t>4725; 14693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10120; 21825</t>
+          <t>9883; 21599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52115; 72344</t>
+          <t>51252; 71272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2842; 10619</t>
+          <t>2078; 10013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1693; 9020</t>
+          <t>1261; 8521</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16769; 29397</t>
+          <t>17376; 29796</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9193; 21675</t>
+          <t>9129; 22372</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13262; 27654</t>
+          <t>14501; 28581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72917; 97280</t>
+          <t>73542; 97381</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4990; 12943</t>
+          <t>5158; 13310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3378; 13736</t>
+          <t>3159; 12812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25686; 42245</t>
+          <t>26184; 41554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5891</t>
+          <t>0; 5886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14363; 24707</t>
+          <t>14612; 24449</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5463; 16232</t>
+          <t>6089; 16257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5557; 16635</t>
+          <t>5403; 17048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43362; 63062</t>
+          <t>42306; 62238</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15071; 26219</t>
+          <t>15161; 26174</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10226; 21279</t>
+          <t>9859; 21326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127953; 319566</t>
+          <t>127581; 316549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2147; 9082</t>
+          <t>2360; 9729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1105; 6349</t>
+          <t>1041; 6354</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9467; 17507</t>
+          <t>9666; 17547</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19759; 33985</t>
+          <t>20523; 33881</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13966; 26695</t>
+          <t>14297; 26570</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139508; 344067</t>
+          <t>141085; 345581</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14090; 26085</t>
+          <t>14138; 26744</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23916; 37123</t>
+          <t>24328; 37653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55936; 77541</t>
+          <t>56805; 78050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6121; 13446</t>
+          <t>6175; 13423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8730; 19237</t>
+          <t>8427; 19016</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24002; 37176</t>
+          <t>24206; 37942</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23240; 37172</t>
+          <t>23262; 37687</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36246; 53653</t>
+          <t>36550; 52653</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85571; 109940</t>
+          <t>85077; 110300</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3076; 8470</t>
+          <t>3117; 8470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7536; 16917</t>
+          <t>7994; 17030</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17723; 30748</t>
+          <t>17043; 30206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12998; 23361</t>
+          <t>12986; 23220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9723; 20434</t>
+          <t>9383; 20402</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29272; 43240</t>
+          <t>29504; 42527</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19073; 30862</t>
+          <t>19264; 30200</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20220; 34528</t>
+          <t>20482; 33636</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51042; 69873</t>
+          <t>50423; 69522</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>401; 3171</t>
+          <t>423; 3150</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15968; 26468</t>
+          <t>15408; 26744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16404; 29499</t>
+          <t>16686; 29658</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44274; 59450</t>
+          <t>44172; 60790</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15968; 26468</t>
+          <t>15408; 26744</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16404; 29499</t>
+          <t>16686; 29658</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46328; 62386</t>
+          <t>46077; 62271</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56432; 78039</t>
+          <t>57249; 77847</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>70282; 95764</t>
+          <t>69928; 95964</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316618; 654518</t>
+          <t>316217; 629454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54746; 76130</t>
+          <t>55380; 75574</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53840; 76011</t>
+          <t>53705; 77115</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159660; 189203</t>
+          <t>159484; 188939</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>116716; 148641</t>
+          <t>117536; 146163</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>131494; 165408</t>
+          <t>129556; 164495</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>486222; 913465</t>
+          <t>482184; 907725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$endoscopia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,67; 76,71</t>
+          <t>21,74; 75,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 69,81</t>
+          <t>32,07; 70,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,95; 55,55</t>
+          <t>40,95; 56,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 74,87</t>
+          <t>21,19; 75,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 76,84</t>
+          <t>11,15; 81,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,59; 40,45</t>
+          <t>23,08; 40,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,07; 68,78</t>
+          <t>30,45; 69,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,5; 68,01</t>
+          <t>31,65; 66,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,41; 48,22</t>
+          <t>36,68; 47,34</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 82,01</t>
+          <t>31,02; 81,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 47,54</t>
+          <t>11,99; 48,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,62; 50,19</t>
+          <t>31,99; 51,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,85</t>
+          <t>0,0; 70,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,24; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 49,9</t>
+          <t>28,98; 49,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,82; 66,25</t>
+          <t>24,63; 67,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,75; 52,84</t>
+          <t>17,88; 52,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 47,23</t>
+          <t>33,77; 48,17</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,76; 89,37</t>
+          <t>50,63; 89,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,76; 73,02</t>
+          <t>36,33; 74,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,65; 95,91</t>
+          <t>33,63; 52,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 89,24</t>
+          <t>20,18; 83,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 86,4</t>
+          <t>14,96; 86,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,66; 53,84</t>
+          <t>29,63; 54,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,07; 84,3</t>
+          <t>51,53; 84,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,11; 72,68</t>
+          <t>36,94; 71,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,9; 95,29</t>
+          <t>34,3; 49,12</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,03; 73,83</t>
+          <t>40,77; 73,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,29; 76,29</t>
+          <t>48,5; 75,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,69; 49,04</t>
+          <t>36,24; 49,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,62; 92,66</t>
+          <t>42,25; 92,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,67; 78,24</t>
+          <t>34,98; 78,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 44,38</t>
+          <t>28,85; 43,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,87; 74,32</t>
+          <t>45,57; 73,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,62; 71,48</t>
+          <t>50,01; 73,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 45,08</t>
+          <t>35,02; 45,42</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,8; 100,0</t>
+          <t>36,24; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,39; 73,27</t>
+          <t>33,68; 73,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,62; 45,41</t>
+          <t>27,22; 47,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,22; 86,22</t>
+          <t>51,34; 87,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 74,43</t>
+          <t>34,19; 73,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,62; 38,37</t>
+          <t>26,18; 38,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,42; 85,31</t>
+          <t>55,51; 84,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,44; 66,41</t>
+          <t>40,2; 68,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,43; 39,2</t>
+          <t>28,74; 39,81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 81,05</t>
+          <t>7,15; 80,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,21; 83,68</t>
+          <t>49,22; 83,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 75,19</t>
+          <t>41,28; 75,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,88; 50,75</t>
+          <t>37,22; 49,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,21; 83,68</t>
+          <t>49,22; 83,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 75,19</t>
+          <t>41,28; 75,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,26; 50,35</t>
+          <t>37,19; 50,8</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,35; 71,18</t>
+          <t>50,73; 71,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,79; 60,1</t>
+          <t>43,78; 59,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,03; 81,67</t>
+          <t>39,34; 47,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,27; 71,32</t>
+          <t>49,66; 70,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,73; 67,11</t>
+          <t>47,17; 66,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,84; 40,08</t>
+          <t>33,82; 40,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,59; 67,88</t>
+          <t>53,94; 67,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,18; 59,9</t>
+          <t>47,52; 60,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,82; 73,08</t>
+          <t>37,91; 42,91</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84976</t>
+          <t>92526</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4725; 14693</t>
+          <t>4164; 14434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9883; 21599</t>
+          <t>9922; 21790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51252; 71272</t>
+          <t>55832; 77202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2078; 10013</t>
+          <t>2834; 10067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1261; 8521</t>
+          <t>1237; 9013</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17376; 29796</t>
+          <t>19178; 33473</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9129; 22372</t>
+          <t>9904; 22659</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14501; 28581</t>
+          <t>13299; 27782</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73542; 97381</t>
+          <t>80488; 103875</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>57201</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5158; 13310</t>
+          <t>5034; 13184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3159; 12812</t>
+          <t>3230; 13096</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26184; 41554</t>
+          <t>27502; 44434</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5886</t>
+          <t>0; 5895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1076; 5316</t>
+          <t>0; 5316</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14612; 24449</t>
+          <t>15943; 27394</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6089; 16257</t>
+          <t>6043; 16518</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5403; 17048</t>
+          <t>5769; 16896</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42306; 62238</t>
+          <t>47615; 67913</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279839</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>293166</t>
+          <t>53666</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15161; 26174</t>
+          <t>14828; 26236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9859; 21326</t>
+          <t>10609; 21689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127581; 316549</t>
+          <t>30751; 48122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2360; 9729</t>
+          <t>2200; 9064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1041; 6354</t>
+          <t>1100; 6350</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9666; 17547</t>
+          <t>10672; 19600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20523; 33881</t>
+          <t>20709; 33993</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14297; 26570</t>
+          <t>13503; 26136</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>141085; 345581</t>
+          <t>43717; 62611</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>74293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96919</t>
+          <t>107968</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14138; 26744</t>
+          <t>14770; 26479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24328; 37653</t>
+          <t>23939; 37318</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56805; 78050</t>
+          <t>63025; 86422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6175; 13423</t>
+          <t>6120; 13420</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8427; 19016</t>
+          <t>8502; 19061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24206; 37942</t>
+          <t>26977; 40338</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23262; 37687</t>
+          <t>23107; 37158</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36550; 52653</t>
+          <t>36839; 53913</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85077; 110300</t>
+          <t>93639; 121459</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59625</t>
+          <t>65207</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3117; 8470</t>
+          <t>3070; 8470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7994; 17030</t>
+          <t>7827; 17029</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17043; 30206</t>
+          <t>19862; 34646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12986; 23220</t>
+          <t>13827; 23607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9383; 20402</t>
+          <t>9373; 20211</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29504; 42527</t>
+          <t>31430; 46181</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19264; 30200</t>
+          <t>19652; 30006</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20482; 33636</t>
+          <t>20364; 34680</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50423; 69522</t>
+          <t>55481; 76851</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52352</t>
+          <t>57815</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53947</t>
+          <t>59429</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>423; 3150</t>
+          <t>275; 3094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15408; 26744</t>
+          <t>15729; 26620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16686; 29658</t>
+          <t>16280; 29760</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44172; 60790</t>
+          <t>49210; 65955</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15408; 26744</t>
+          <t>15729; 26620</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16686; 29658</t>
+          <t>16280; 29760</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46077; 62271</t>
+          <t>50599; 69119</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>467419</t>
+          <t>244162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>173940</t>
+          <t>191835</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>641359</t>
+          <t>435997</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57249; 77847</t>
+          <t>55486; 78290</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69928; 95964</t>
+          <t>69918; 94738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316217; 629454</t>
+          <t>222049; 265783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55380; 75574</t>
+          <t>52621; 74467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53705; 77115</t>
+          <t>54208; 76144</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159484; 188939</t>
+          <t>175819; 210647</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>117536; 146163</t>
+          <t>116152; 145971</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>129556; 164495</t>
+          <t>130491; 164755</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>482184; 907725</t>
+          <t>411071; 465325</t>
         </is>
       </c>
     </row>
